--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run9/epoch_20/per_file_predictions_epoch_20.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run9/epoch_20/per_file_predictions_epoch_20.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="477">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="479">
   <si>
     <t>Filename</t>
   </si>
@@ -808,643 +808,649 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9772,0.0019,0.0192,0.0002</t>
-  </si>
-  <si>
-    <t>0.1230,0.0003,0.0609,0.7590</t>
-  </si>
-  <si>
-    <t>0.9868,0.0010,0.0046,0.0009</t>
-  </si>
-  <si>
-    <t>0.7772,0.0008,0.1024,0.0296</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0.9817,0.0017,0.0136,0.0002</t>
+  </si>
+  <si>
+    <t>0.3442,0.0002,0.0665,0.3749</t>
+  </si>
+  <si>
+    <t>0.9675,0.0009,0.0158,0.0021</t>
+  </si>
+  <si>
+    <t>0.7777,0.0011,0.1088,0.0312</t>
   </si>
   <si>
     <t>0.9997,0.0001,0.0000,0.0000</t>
   </si>
   <si>
+    <t>0.9994,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
     <t>0.9996,0.0002,0.0000,0.0000</t>
   </si>
   <si>
     <t>0.9998,0.0001,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.7491,0.0015,0.3388,0.0010</t>
-  </si>
-  <si>
-    <t>0.3842,0.0005,0.8052,0.0001</t>
-  </si>
-  <si>
-    <t>0.5458,0.0013,0.6218,0.0002</t>
-  </si>
-  <si>
-    <t>0.0725,0.0006,0.9593,0.0003</t>
-  </si>
-  <si>
-    <t>0.7252,0.0013,0.4115,0.0007</t>
-  </si>
-  <si>
-    <t>0.0026,0.9951,0.0064,0.0001</t>
-  </si>
-  <si>
-    <t>0.0949,0.8812,0.0245,0.0003</t>
-  </si>
-  <si>
-    <t>0.3786,0.5858,0.0260,0.0003</t>
-  </si>
-  <si>
-    <t>0.1761,0.8299,0.0135,0.0004</t>
-  </si>
-  <si>
-    <t>0.0051,0.9918,0.0063,0.0000</t>
-  </si>
-  <si>
-    <t>0.5351,0.0004,0.6224,0.0008</t>
-  </si>
-  <si>
-    <t>0.3231,0.0007,0.7840,0.0011</t>
-  </si>
-  <si>
-    <t>0.1141,0.0005,0.9424,0.0002</t>
-  </si>
-  <si>
-    <t>0.4671,0.0007,0.7025,0.0003</t>
-  </si>
-  <si>
-    <t>0.0835,0.0003,0.9563,0.0002</t>
-  </si>
-  <si>
-    <t>0.0773,0.0003,0.9580,0.0002</t>
-  </si>
-  <si>
-    <t>0.0100,0.0001,0.9911,0.0007</t>
-  </si>
-  <si>
-    <t>0.8990,0.0556,0.0224,0.0003</t>
-  </si>
-  <si>
-    <t>0.9278,0.0124,0.0493,0.0005</t>
-  </si>
-  <si>
-    <t>0.0005,0.0019,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0153,0.1007,0.9650,0.0003</t>
-  </si>
-  <si>
-    <t>0.9589,0.0076,0.0279,0.0003</t>
-  </si>
-  <si>
-    <t>0.9214,0.0058,0.0829,0.0002</t>
-  </si>
-  <si>
-    <t>0.9795,0.0178,0.0023,0.0001</t>
-  </si>
-  <si>
-    <t>0.0733,0.7088,0.2749,0.0007</t>
-  </si>
-  <si>
-    <t>0.0037,0.7958,0.7779,0.0007</t>
-  </si>
-  <si>
-    <t>0.0245,0.0013,0.9764,0.0008</t>
-  </si>
-  <si>
-    <t>0.0172,0.0028,0.9851,0.0002</t>
-  </si>
-  <si>
-    <t>0.0572,0.0003,0.9641,0.0004</t>
-  </si>
-  <si>
-    <t>0.0918,0.0051,0.9302,0.0001</t>
-  </si>
-  <si>
-    <t>0.0008,0.9936,0.0405,0.0002</t>
-  </si>
-  <si>
-    <t>0.0057,0.0016,0.9961,0.0001</t>
-  </si>
-  <si>
-    <t>0.5650,0.0180,0.3504,0.0382</t>
-  </si>
-  <si>
-    <t>0.0023,0.9885,0.0026,0.0210</t>
-  </si>
-  <si>
-    <t>0.0015,0.9860,0.1156,0.0006</t>
-  </si>
-  <si>
-    <t>0.0001,0.9990,0.0019,0.0004</t>
-  </si>
-  <si>
-    <t>0.0001,0.0573,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.0426,0.9981,0.0001</t>
-  </si>
-  <si>
-    <t>0.0261,0.0007,0.9832,0.0003</t>
-  </si>
-  <si>
-    <t>0.0392,0.0003,0.9816,0.0001</t>
-  </si>
-  <si>
-    <t>0.0077,0.0006,0.9939,0.0003</t>
-  </si>
-  <si>
-    <t>0.0020,0.0008,0.9977,0.0004</t>
-  </si>
-  <si>
-    <t>0.9990,0.0005,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9987,0.0004,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9979,0.0007,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0031,0.0029,0.9985,0.0001</t>
+    <t>0.8534,0.0033,0.1592,0.0008</t>
+  </si>
+  <si>
+    <t>0.2613,0.0016,0.8606,0.0002</t>
+  </si>
+  <si>
+    <t>0.7592,0.0013,0.3647,0.0003</t>
+  </si>
+  <si>
+    <t>0.2478,0.0009,0.8429,0.0007</t>
+  </si>
+  <si>
+    <t>0.6985,0.0014,0.4503,0.0009</t>
+  </si>
+  <si>
+    <t>0.0063,0.9916,0.0030,0.0001</t>
+  </si>
+  <si>
+    <t>0.0604,0.9366,0.0090,0.0002</t>
+  </si>
+  <si>
+    <t>0.6627,0.3458,0.0132,0.0002</t>
+  </si>
+  <si>
+    <t>0.1192,0.8737,0.0157,0.0003</t>
+  </si>
+  <si>
+    <t>0.0023,0.9961,0.0031,0.0000</t>
+  </si>
+  <si>
+    <t>0.4974,0.0006,0.6450,0.0010</t>
+  </si>
+  <si>
+    <t>0.3017,0.0003,0.8142,0.0008</t>
+  </si>
+  <si>
+    <t>0.2789,0.0006,0.8529,0.0002</t>
+  </si>
+  <si>
+    <t>0.3449,0.0005,0.7895,0.0006</t>
+  </si>
+  <si>
+    <t>0.0368,0.0009,0.9804,0.0001</t>
+  </si>
+  <si>
+    <t>0.0349,0.0006,0.9787,0.0001</t>
+  </si>
+  <si>
+    <t>0.0218,0.0001,0.9812,0.0011</t>
+  </si>
+  <si>
+    <t>0.8929,0.0179,0.0692,0.0005</t>
+  </si>
+  <si>
+    <t>0.8050,0.0071,0.2258,0.0008</t>
+  </si>
+  <si>
+    <t>0.0004,0.0030,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0355,0.1582,0.8925,0.0006</t>
+  </si>
+  <si>
+    <t>0.9122,0.0130,0.0680,0.0007</t>
+  </si>
+  <si>
+    <t>0.3299,0.0194,0.6919,0.0004</t>
+  </si>
+  <si>
+    <t>0.9554,0.0480,0.0024,0.0000</t>
+  </si>
+  <si>
+    <t>0.0431,0.7108,0.4124,0.0005</t>
+  </si>
+  <si>
+    <t>0.0127,0.3877,0.8941,0.0008</t>
+  </si>
+  <si>
+    <t>0.0062,0.0074,0.9909,0.0006</t>
+  </si>
+  <si>
+    <t>0.0071,0.0226,0.9894,0.0002</t>
+  </si>
+  <si>
+    <t>0.2165,0.0005,0.8729,0.0004</t>
+  </si>
+  <si>
+    <t>0.0661,0.0189,0.9222,0.0002</t>
+  </si>
+  <si>
+    <t>0.0021,0.9857,0.0274,0.0015</t>
+  </si>
+  <si>
+    <t>0.0023,0.0061,0.9973,0.0001</t>
+  </si>
+  <si>
+    <t>0.6143,0.0060,0.3844,0.0156</t>
+  </si>
+  <si>
+    <t>0.0005,0.9959,0.0021,0.0090</t>
+  </si>
+  <si>
+    <t>0.0045,0.9691,0.1321,0.0018</t>
+  </si>
+  <si>
+    <t>0.0012,0.9945,0.0107,0.0014</t>
+  </si>
+  <si>
+    <t>0.0006,0.0062,0.9992,0.0000</t>
+  </si>
+  <si>
+    <t>0.0031,0.0257,0.9948,0.0001</t>
+  </si>
+  <si>
+    <t>0.0348,0.0007,0.9801,0.0002</t>
+  </si>
+  <si>
+    <t>0.0343,0.0003,0.9849,0.0001</t>
+  </si>
+  <si>
+    <t>0.0040,0.0003,0.9964,0.0003</t>
+  </si>
+  <si>
+    <t>0.0022,0.0004,0.9978,0.0002</t>
+  </si>
+  <si>
+    <t>0.9987,0.0005,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9990,0.0003,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0060,0.0017,0.9978,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0002,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0005,0.0001,0.0000</t>
   </si>
   <si>
     <t>0.9991,0.0004,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.9992,0.0004,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9984,0.0007,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.8480,0.9961,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.0119,0.9990,0.0000</t>
-  </si>
-  <si>
-    <t>0.0040,0.0022,0.9956,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9351,0.9929,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.0002,0.9993,0.0001</t>
-  </si>
-  <si>
-    <t>0.0233,0.9660,0.0153,0.0003</t>
-  </si>
-  <si>
-    <t>0.0003,0.9994,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.8810,0.0039,0.1526,0.0004</t>
-  </si>
-  <si>
-    <t>0.8209,0.0020,0.2720,0.0004</t>
-  </si>
-  <si>
-    <t>0.0007,0.0075,0.9994,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.8307,0.9754,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.3901,0.9971,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9925,0.5430,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9977,0.4504,0.0000</t>
-  </si>
-  <si>
-    <t>0.1045,0.0002,0.1767,0.5519</t>
-  </si>
-  <si>
-    <t>0.0020,0.0001,0.0019,0.9977</t>
-  </si>
-  <si>
-    <t>0.0197,0.0002,0.0108,0.9736</t>
-  </si>
-  <si>
-    <t>0.4890,0.0013,0.2125,0.1128</t>
-  </si>
-  <si>
-    <t>0.0660,0.0003,0.1178,0.7604</t>
-  </si>
-  <si>
-    <t>0.0125,0.0002,0.0143,0.9808</t>
-  </si>
-  <si>
-    <t>0.0000,0.9678,0.9843,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9596,0.9581,0.0000</t>
-  </si>
-  <si>
-    <t>0.0033,0.7929,0.8486,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.4972,0.9964,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9480,0.9529,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.8601,0.9664,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0003,0.0000,0.0000</t>
+    <t>0.0001,0.9264,0.9729,0.0000</t>
+  </si>
+  <si>
+    <t>0.0011,0.0073,0.9986,0.0001</t>
+  </si>
+  <si>
+    <t>0.0095,0.0103,0.9880,0.0005</t>
+  </si>
+  <si>
+    <t>0.0000,0.9552,0.9954,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.0002,0.9991,0.0002</t>
+  </si>
+  <si>
+    <t>0.0305,0.9648,0.0075,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9222,0.0013,0.1349,0.0002</t>
+  </si>
+  <si>
+    <t>0.8979,0.0024,0.1489,0.0001</t>
+  </si>
+  <si>
+    <t>0.0008,0.0022,0.9994,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9635,0.9731,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.7327,0.9799,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9970,0.3212,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9942,0.6125,0.0000</t>
+  </si>
+  <si>
+    <t>0.2302,0.0003,0.3942,0.1240</t>
+  </si>
+  <si>
+    <t>0.0040,0.0001,0.0025,0.9960</t>
+  </si>
+  <si>
+    <t>0.1141,0.0004,0.1144,0.6277</t>
+  </si>
+  <si>
+    <t>0.4277,0.0012,0.2608,0.1287</t>
+  </si>
+  <si>
+    <t>0.0699,0.0002,0.1138,0.7316</t>
+  </si>
+  <si>
+    <t>0.0158,0.0002,0.0127,0.9775</t>
+  </si>
+  <si>
+    <t>0.0001,0.9624,0.9528,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9164,0.9926,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.8150,0.9881,0.0000</t>
+  </si>
+  <si>
+    <t>0.0008,0.2819,0.9922,0.0002</t>
+  </si>
+  <si>
+    <t>0.0004,0.8442,0.9617,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9793,0.9150,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0003,0.0000,0.0000</t>
   </si>
   <si>
     <t>0.9995,0.0002,0.0000,0.0000</t>
   </si>
   <si>
+    <t>0.9994,0.0003,0.0001,0.0000</t>
+  </si>
+  <si>
     <t>0.9996,0.0001,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.0004,0.0007,0.9995,0.0001</t>
-  </si>
-  <si>
-    <t>0.0611,0.0013,0.9672,0.0002</t>
-  </si>
-  <si>
-    <t>0.6426,0.0022,0.4655,0.0014</t>
-  </si>
-  <si>
-    <t>0.0752,0.0004,0.9562,0.0003</t>
-  </si>
-  <si>
-    <t>0.0552,0.9464,0.0048,0.0001</t>
-  </si>
-  <si>
-    <t>0.0409,0.9446,0.0176,0.0001</t>
-  </si>
-  <si>
-    <t>0.9356,0.0769,0.0029,0.0001</t>
-  </si>
-  <si>
-    <t>0.4695,0.5398,0.0185,0.0004</t>
-  </si>
-  <si>
-    <t>0.0252,0.9616,0.0177,0.0001</t>
-  </si>
-  <si>
-    <t>0.0041,0.9936,0.0044,0.0000</t>
-  </si>
-  <si>
-    <t>0.7348,0.2965,0.0100,0.0002</t>
-  </si>
-  <si>
-    <t>0.7858,0.0073,0.2332,0.0008</t>
-  </si>
-  <si>
-    <t>0.4543,0.0017,0.6813,0.0005</t>
-  </si>
-  <si>
-    <t>0.5092,0.0067,0.5641,0.0007</t>
-  </si>
-  <si>
-    <t>0.5815,0.0070,0.4940,0.0012</t>
-  </si>
-  <si>
-    <t>0.2758,0.0024,0.3820,0.1883</t>
-  </si>
-  <si>
-    <t>0.0005,0.9978,0.0019,0.0010</t>
-  </si>
-  <si>
-    <t>0.0001,0.9996,0.0004,0.0004</t>
-  </si>
-  <si>
-    <t>0.0939,0.8457,0.0541,0.0059</t>
-  </si>
-  <si>
-    <t>0.0000,0.9965,0.9347,0.0000</t>
-  </si>
-  <si>
-    <t>0.2164,0.7142,0.0366,0.0002</t>
-  </si>
-  <si>
-    <t>0.9773,0.0178,0.0032,0.0001</t>
-  </si>
-  <si>
-    <t>0.9577,0.0408,0.0032,0.0001</t>
-  </si>
-  <si>
-    <t>0.9972,0.0017,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9990,0.0003,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9988,0.0002,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9974,0.0015,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0002,0.0001,0.0000</t>
+    <t>0.0017,0.0009,0.9985,0.0001</t>
+  </si>
+  <si>
+    <t>0.0286,0.0029,0.9818,0.0001</t>
+  </si>
+  <si>
+    <t>0.6531,0.0041,0.4216,0.0020</t>
+  </si>
+  <si>
+    <t>0.0063,0.0011,0.9958,0.0001</t>
+  </si>
+  <si>
+    <t>0.0327,0.9628,0.0067,0.0001</t>
+  </si>
+  <si>
+    <t>0.0349,0.9369,0.0354,0.0001</t>
+  </si>
+  <si>
+    <t>0.9132,0.1131,0.0027,0.0001</t>
+  </si>
+  <si>
+    <t>0.2961,0.6770,0.0250,0.0003</t>
+  </si>
+  <si>
+    <t>0.0152,0.9757,0.0146,0.0001</t>
+  </si>
+  <si>
+    <t>0.0052,0.9906,0.0102,0.0001</t>
+  </si>
+  <si>
+    <t>0.9269,0.0576,0.0117,0.0003</t>
+  </si>
+  <si>
+    <t>0.4308,0.0019,0.6990,0.0011</t>
+  </si>
+  <si>
+    <t>0.2477,0.0012,0.8644,0.0002</t>
+  </si>
+  <si>
+    <t>0.5233,0.0079,0.5417,0.0006</t>
+  </si>
+  <si>
+    <t>0.4132,0.0764,0.4419,0.0026</t>
+  </si>
+  <si>
+    <t>0.2123,0.0252,0.2182,0.4222</t>
+  </si>
+  <si>
+    <t>0.0018,0.9932,0.0073,0.0029</t>
+  </si>
+  <si>
+    <t>0.0001,0.9993,0.0007,0.0017</t>
+  </si>
+  <si>
+    <t>0.0150,0.9661,0.0173,0.0038</t>
+  </si>
+  <si>
+    <t>0.0000,0.9970,0.9205,0.0000</t>
+  </si>
+  <si>
+    <t>0.0886,0.8622,0.0389,0.0002</t>
+  </si>
+  <si>
+    <t>0.9699,0.0206,0.0056,0.0001</t>
+  </si>
+  <si>
+    <t>0.9903,0.0059,0.0015,0.0001</t>
+  </si>
+  <si>
+    <t>0.9979,0.0014,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9989,0.0003,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9989,0.0002,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9962,0.0020,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.0014,0.0520,0.9961,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.3475,0.9988,0.0000</t>
+  </si>
+  <si>
+    <t>0.0048,0.0097,0.9930,0.0004</t>
+  </si>
+  <si>
+    <t>0.0096,0.0020,0.9920,0.0002</t>
+  </si>
+  <si>
+    <t>0.7594,0.0013,0.3217,0.0013</t>
+  </si>
+  <si>
+    <t>0.7150,0.0021,0.4016,0.0009</t>
+  </si>
+  <si>
+    <t>0.5042,0.0006,0.6603,0.0011</t>
+  </si>
+  <si>
+    <t>0.7186,0.0022,0.3904,0.0006</t>
+  </si>
+  <si>
+    <t>0.8275,0.0005,0.0194,0.0640</t>
+  </si>
+  <si>
+    <t>0.0011,0.0000,0.0057,0.9974</t>
+  </si>
+  <si>
+    <t>0.0222,0.0006,0.0128,0.9715</t>
+  </si>
+  <si>
+    <t>0.0383,0.0002,0.0379,0.9250</t>
+  </si>
+  <si>
+    <t>0.0000,0.9979,0.7858,0.0000</t>
+  </si>
+  <si>
+    <t>0.9990,0.0004,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9809,0.0129,0.0030,0.0002</t>
+  </si>
+  <si>
+    <t>0.9990,0.0002,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9825,0.0130,0.0028,0.0001</t>
+  </si>
+  <si>
+    <t>0.8290,0.0017,0.1374,0.0064</t>
+  </si>
+  <si>
+    <t>0.0124,0.0005,0.9826,0.0046</t>
+  </si>
+  <si>
+    <t>0.9921,0.0006,0.0055,0.0001</t>
+  </si>
+  <si>
+    <t>0.9957,0.0007,0.0018,0.0001</t>
+  </si>
+  <si>
+    <t>0.8859,0.1129,0.0117,0.0005</t>
+  </si>
+  <si>
+    <t>0.9689,0.0040,0.0222,0.0003</t>
+  </si>
+  <si>
+    <t>0.9858,0.0017,0.0101,0.0001</t>
+  </si>
+  <si>
+    <t>0.8996,0.0339,0.0405,0.0013</t>
+  </si>
+  <si>
+    <t>0.9558,0.0038,0.0448,0.0002</t>
+  </si>
+  <si>
+    <t>0.9046,0.0057,0.0978,0.0004</t>
   </si>
   <si>
     <t>0.9993,0.0002,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.0001,0.8003,0.9926,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.1245,0.9984,0.0000</t>
-  </si>
-  <si>
-    <t>0.0013,0.0393,0.9969,0.0001</t>
-  </si>
-  <si>
-    <t>0.0195,0.0008,0.9846,0.0003</t>
-  </si>
-  <si>
-    <t>0.7228,0.0028,0.3562,0.0014</t>
-  </si>
-  <si>
-    <t>0.7150,0.0022,0.3926,0.0009</t>
-  </si>
-  <si>
-    <t>0.4356,0.0004,0.7475,0.0005</t>
-  </si>
-  <si>
-    <t>0.6576,0.0026,0.4602,0.0007</t>
-  </si>
-  <si>
-    <t>0.8688,0.0020,0.0439,0.0193</t>
-  </si>
-  <si>
-    <t>0.0004,0.0000,0.0030,0.9990</t>
-  </si>
-  <si>
-    <t>0.0147,0.0006,0.0207,0.9742</t>
-  </si>
-  <si>
-    <t>0.0239,0.0001,0.0245,0.9578</t>
-  </si>
-  <si>
-    <t>0.0000,0.9977,0.6259,0.0000</t>
+    <t>0.9557,0.0241,0.0116,0.0003</t>
+  </si>
+  <si>
+    <t>0.9873,0.0117,0.0010,0.0000</t>
+  </si>
+  <si>
+    <t>0.9248,0.0783,0.0059,0.0001</t>
+  </si>
+  <si>
+    <t>0.9851,0.0023,0.0089,0.0002</t>
+  </si>
+  <si>
+    <t>0.9978,0.0012,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9932,0.0035,0.0014,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0003,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9969,0.0012,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.0016,0.0011,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.9960,0.0008,0.0015,0.0001</t>
+  </si>
+  <si>
+    <t>0.0023,0.0005,0.9985,0.0000</t>
+  </si>
+  <si>
+    <t>0.0053,0.0029,0.9957,0.0001</t>
+  </si>
+  <si>
+    <t>0.0285,0.0002,0.9826,0.0003</t>
+  </si>
+  <si>
+    <t>0.0011,0.0073,0.9980,0.0003</t>
+  </si>
+  <si>
+    <t>0.0107,0.0010,0.9920,0.0002</t>
+  </si>
+  <si>
+    <t>0.0347,0.0003,0.9834,0.0001</t>
+  </si>
+  <si>
+    <t>0.0034,0.0006,0.9968,0.0004</t>
+  </si>
+  <si>
+    <t>0.5489,0.0021,0.5963,0.0004</t>
+  </si>
+  <si>
+    <t>0.1360,0.0009,0.9293,0.0002</t>
+  </si>
+  <si>
+    <t>0.7580,0.0083,0.2583,0.0013</t>
+  </si>
+  <si>
+    <t>0.4872,0.0024,0.6365,0.0005</t>
+  </si>
+  <si>
+    <t>0.4094,0.0057,0.6647,0.0005</t>
+  </si>
+  <si>
+    <t>0.5752,0.0026,0.5537,0.0002</t>
+  </si>
+  <si>
+    <t>0.6658,0.0037,0.4078,0.0023</t>
+  </si>
+  <si>
+    <t>0.4580,0.0017,0.6928,0.0003</t>
+  </si>
+  <si>
+    <t>0.9598,0.0466,0.0023,0.0001</t>
+  </si>
+  <si>
+    <t>0.9898,0.0109,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.9898,0.0088,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.9989,0.0005,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9984,0.0009,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.7227,0.0042,0.3469,0.0010</t>
+  </si>
+  <si>
+    <t>0.6836,0.0012,0.4656,0.0005</t>
+  </si>
+  <si>
+    <t>0.7548,0.0061,0.2891,0.0014</t>
+  </si>
+  <si>
+    <t>0.5680,0.0013,0.5745,0.0009</t>
+  </si>
+  <si>
+    <t>0.6892,0.0020,0.4262,0.0012</t>
+  </si>
+  <si>
+    <t>0.0072,0.0012,0.9953,0.0003</t>
+  </si>
+  <si>
+    <t>0.0085,0.0079,0.9898,0.0003</t>
+  </si>
+  <si>
+    <t>0.0096,0.0211,0.9858,0.0002</t>
+  </si>
+  <si>
+    <t>0.0403,0.0038,0.9678,0.0002</t>
+  </si>
+  <si>
+    <t>0.0005,0.0057,0.9991,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0003,0.0001,0.0000</t>
   </si>
   <si>
     <t>0.9992,0.0003,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.9059,0.1052,0.0066,0.0002</t>
-  </si>
-  <si>
-    <t>0.9986,0.0003,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9659,0.0305,0.0040,0.0001</t>
-  </si>
-  <si>
-    <t>0.9727,0.0013,0.0175,0.0007</t>
-  </si>
-  <si>
-    <t>0.9989,0.0002,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0097,0.0014,0.9895,0.0014</t>
-  </si>
-  <si>
-    <t>0.9874,0.0007,0.0106,0.0001</t>
-  </si>
-  <si>
-    <t>0.9953,0.0006,0.0020,0.0001</t>
-  </si>
-  <si>
-    <t>0.5665,0.2218,0.1143,0.0011</t>
-  </si>
-  <si>
-    <t>0.9806,0.0024,0.0136,0.0001</t>
-  </si>
-  <si>
-    <t>0.9630,0.0025,0.0404,0.0001</t>
-  </si>
-  <si>
-    <t>0.6476,0.2833,0.0439,0.0011</t>
-  </si>
-  <si>
-    <t>0.9453,0.0050,0.0511,0.0004</t>
-  </si>
-  <si>
-    <t>0.8839,0.0080,0.1160,0.0005</t>
-  </si>
-  <si>
-    <t>0.9995,0.0002,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9833,0.0116,0.0021,0.0001</t>
-  </si>
-  <si>
-    <t>0.9777,0.0221,0.0019,0.0001</t>
-  </si>
-  <si>
-    <t>0.9685,0.0319,0.0023,0.0001</t>
-  </si>
-  <si>
-    <t>0.9879,0.0027,0.0057,0.0002</t>
-  </si>
-  <si>
-    <t>0.9967,0.0012,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.9990,0.0003,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9968,0.0012,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.0020,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.9981,0.0004,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0059,0.0004,0.9966,0.0001</t>
-  </si>
-  <si>
-    <t>0.0190,0.0034,0.9865,0.0001</t>
-  </si>
-  <si>
-    <t>0.1519,0.0003,0.9195,0.0004</t>
-  </si>
-  <si>
-    <t>0.0009,0.0159,0.9981,0.0003</t>
-  </si>
-  <si>
-    <t>0.0066,0.0026,0.9950,0.0001</t>
-  </si>
-  <si>
-    <t>0.0159,0.0003,0.9907,0.0001</t>
-  </si>
-  <si>
-    <t>0.0103,0.0013,0.9939,0.0001</t>
-  </si>
-  <si>
-    <t>0.2505,0.0029,0.8389,0.0004</t>
-  </si>
-  <si>
-    <t>0.1423,0.0006,0.9290,0.0002</t>
-  </si>
-  <si>
-    <t>0.3928,0.0023,0.7379,0.0010</t>
-  </si>
-  <si>
-    <t>0.5841,0.0013,0.5657,0.0004</t>
-  </si>
-  <si>
-    <t>0.2892,0.0072,0.7735,0.0004</t>
-  </si>
-  <si>
-    <t>0.6677,0.0023,0.4725,0.0003</t>
-  </si>
-  <si>
-    <t>0.3033,0.0039,0.7797,0.0015</t>
-  </si>
-  <si>
-    <t>0.6447,0.0021,0.4934,0.0006</t>
-  </si>
-  <si>
-    <t>0.9796,0.0198,0.0019,0.0001</t>
-  </si>
-  <si>
-    <t>0.9485,0.0601,0.0031,0.0001</t>
-  </si>
-  <si>
-    <t>0.9950,0.0037,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0005,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9960,0.0029,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.6648,0.0029,0.4125,0.0021</t>
-  </si>
-  <si>
-    <t>0.7621,0.0011,0.3620,0.0005</t>
-  </si>
-  <si>
-    <t>0.8127,0.0017,0.2535,0.0007</t>
-  </si>
-  <si>
-    <t>0.5944,0.0021,0.5405,0.0006</t>
-  </si>
-  <si>
-    <t>0.6362,0.0017,0.4720,0.0020</t>
-  </si>
-  <si>
-    <t>0.0126,0.0017,0.9930,0.0001</t>
-  </si>
-  <si>
-    <t>0.0052,0.0026,0.9937,0.0004</t>
-  </si>
-  <si>
-    <t>0.0107,0.0185,0.9842,0.0005</t>
-  </si>
-  <si>
-    <t>0.0635,0.0010,0.9616,0.0002</t>
-  </si>
-  <si>
-    <t>0.0006,0.0223,0.9985,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0003,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0768,0.0009,0.9590,0.0005</t>
-  </si>
-  <si>
-    <t>0.5429,0.0075,0.5502,0.0012</t>
-  </si>
-  <si>
-    <t>0.9336,0.0021,0.0778,0.0005</t>
-  </si>
-  <si>
-    <t>0.0012,0.0060,0.9989,0.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.0036,0.9991,0.0001</t>
-  </si>
-  <si>
-    <t>0.0073,0.0031,0.9939,0.0001</t>
-  </si>
-  <si>
-    <t>0.0006,0.0009,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0399,0.0035,0.9713,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0039,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0051,0.0016,0.9950,0.0002</t>
-  </si>
-  <si>
-    <t>0.0103,0.0020,0.9920,0.0002</t>
-  </si>
-  <si>
-    <t>0.5722,0.0008,0.5826,0.0011</t>
-  </si>
-  <si>
-    <t>0.6348,0.0014,0.4997,0.0009</t>
-  </si>
-  <si>
-    <t>0.7689,0.0012,0.3141,0.0009</t>
-  </si>
-  <si>
-    <t>0.9995,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.1053,0.0036,0.9173,0.0003</t>
-  </si>
-  <si>
-    <t>0.0013,0.0103,0.9979,0.0001</t>
-  </si>
-  <si>
-    <t>0.0015,0.0241,0.9975,0.0000</t>
-  </si>
-  <si>
-    <t>0.0249,0.0747,0.9411,0.0007</t>
-  </si>
-  <si>
-    <t>0.0146,0.0008,0.9911,0.0001</t>
-  </si>
-  <si>
-    <t>0.1178,0.0012,0.9242,0.0007</t>
-  </si>
-  <si>
-    <t>0.0752,0.0021,0.9464,0.0004</t>
-  </si>
-  <si>
-    <t>0.0806,0.0008,0.9411,0.0009</t>
-  </si>
-  <si>
-    <t>0.9937,0.0007,0.0025,0.0002</t>
-  </si>
-  <si>
-    <t>0.3451,0.0014,0.1473,0.2655</t>
-  </si>
-  <si>
-    <t>0.8668,0.0008,0.0474,0.0192</t>
-  </si>
-  <si>
-    <t>0.0076,0.0001,0.0078,0.9892</t>
-  </si>
-  <si>
-    <t>0.0082,0.0001,0.0031,0.9926</t>
-  </si>
-  <si>
-    <t>0.7718,0.0018,0.2723,0.0022</t>
+    <t>0.0470,0.0013,0.9758,0.0003</t>
+  </si>
+  <si>
+    <t>0.5938,0.0109,0.4650,0.0009</t>
+  </si>
+  <si>
+    <t>0.9849,0.0013,0.0120,0.0001</t>
+  </si>
+  <si>
+    <t>0.0011,0.0029,0.9991,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0048,0.9994,0.0001</t>
+  </si>
+  <si>
+    <t>0.0035,0.1286,0.9865,0.0002</t>
+  </si>
+  <si>
+    <t>0.0030,0.0009,0.9981,0.0000</t>
+  </si>
+  <si>
+    <t>0.0389,0.0011,0.9768,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0029,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0033,0.0048,0.9960,0.0001</t>
+  </si>
+  <si>
+    <t>0.0206,0.0029,0.9834,0.0003</t>
+  </si>
+  <si>
+    <t>0.5922,0.0011,0.5594,0.0011</t>
+  </si>
+  <si>
+    <t>0.4816,0.0008,0.6635,0.0010</t>
+  </si>
+  <si>
+    <t>0.7837,0.0013,0.3065,0.0006</t>
+  </si>
+  <si>
+    <t>0.0563,0.0075,0.9459,0.0003</t>
+  </si>
+  <si>
+    <t>0.0014,0.0033,0.9985,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0231,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0181,0.0188,0.9771,0.0002</t>
+  </si>
+  <si>
+    <t>0.0075,0.0004,0.9944,0.0002</t>
+  </si>
+  <si>
+    <t>0.1758,0.0007,0.8870,0.0011</t>
+  </si>
+  <si>
+    <t>0.2764,0.0006,0.8457,0.0004</t>
+  </si>
+  <si>
+    <t>0.0285,0.0005,0.9743,0.0011</t>
+  </si>
+  <si>
+    <t>0.9933,0.0005,0.0026,0.0003</t>
+  </si>
+  <si>
+    <t>0.3019,0.0009,0.2307,0.2169</t>
+  </si>
+  <si>
+    <t>0.6637,0.0006,0.0310,0.1695</t>
+  </si>
+  <si>
+    <t>0.0059,0.0001,0.0053,0.9928</t>
+  </si>
+  <si>
+    <t>0.0061,0.0001,0.0045,0.9932</t>
+  </si>
+  <si>
+    <t>0.7281,0.0013,0.2321,0.0142</t>
   </si>
 </sst>
 </file>
@@ -1830,7 +1836,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1841,10 +1847,10 @@
         <v>260</v>
       </c>
       <c r="C3" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1858,7 +1864,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1872,7 +1878,7 @@
         <v>259</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1886,7 +1892,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1900,7 +1906,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1914,7 +1920,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1928,7 +1934,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1942,7 +1948,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1956,7 +1962,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1984,7 +1990,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1998,7 +2004,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2012,7 +2018,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2023,10 +2029,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D16" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2040,7 +2046,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2054,7 +2060,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2068,7 +2074,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2082,7 +2088,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2093,10 +2099,10 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D21" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2110,7 +2116,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2124,7 +2130,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2138,7 +2144,7 @@
         <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2152,7 +2158,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2166,7 +2172,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2180,7 +2186,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2194,7 +2200,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2208,7 +2214,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2222,7 +2228,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2236,7 +2242,7 @@
         <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2250,7 +2256,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2264,7 +2270,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2278,7 +2284,7 @@
         <v>261</v>
       </c>
       <c r="D34" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2292,7 +2298,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2303,10 +2309,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D36" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2320,7 +2326,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2334,7 +2340,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2345,10 +2351,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2362,7 +2368,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2376,7 +2382,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2390,7 +2396,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2404,7 +2410,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2418,7 +2424,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2432,7 +2438,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2446,7 +2452,7 @@
         <v>259</v>
       </c>
       <c r="D46" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2460,7 +2466,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2474,7 +2480,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2488,7 +2494,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2502,7 +2508,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2516,7 +2522,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2530,7 +2536,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2544,7 +2550,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2558,7 +2564,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2572,7 +2578,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2586,7 +2592,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2600,7 +2606,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2614,7 +2620,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2628,7 +2634,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2642,7 +2648,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2656,7 +2662,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2670,7 +2676,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2684,7 +2690,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2698,7 +2704,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2712,7 +2718,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2726,7 +2732,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2740,7 +2746,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2754,7 +2760,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2768,7 +2774,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2782,7 +2788,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2796,7 +2802,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2810,7 +2816,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2824,7 +2830,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2835,10 +2841,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2849,10 +2855,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2863,10 +2869,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2877,10 +2883,10 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D77" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2894,7 +2900,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2908,7 +2914,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2919,10 +2925,10 @@
         <v>260</v>
       </c>
       <c r="C80" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D80" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2936,7 +2942,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2950,7 +2956,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2964,7 +2970,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -2978,7 +2984,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -2992,7 +2998,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3006,7 +3012,7 @@
         <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3020,7 +3026,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3034,7 +3040,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3048,7 +3054,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3062,7 +3068,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>269</v>
+        <v>350</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3076,7 +3082,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>318</v>
+        <v>351</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3090,7 +3096,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3104,7 +3110,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3132,7 +3138,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>347</v>
+        <v>272</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3146,7 +3152,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>269</v>
+        <v>350</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3160,7 +3166,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3174,7 +3180,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>347</v>
+        <v>270</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3188,7 +3194,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3202,7 +3208,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3216,7 +3222,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3244,7 +3250,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>270</v>
+        <v>350</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3258,7 +3264,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3272,7 +3278,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3286,7 +3292,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3300,7 +3306,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3314,7 +3320,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3328,7 +3334,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3342,7 +3348,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3356,7 +3362,7 @@
         <v>259</v>
       </c>
       <c r="D111" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3370,7 +3376,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3384,7 +3390,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3398,7 +3404,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3412,7 +3418,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3423,10 +3429,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D116" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3440,7 +3446,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3451,10 +3457,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D118" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3465,10 +3471,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D119" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3479,10 +3485,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D120" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3496,7 +3502,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3510,7 +3516,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3524,7 +3530,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3538,7 +3544,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3552,7 +3558,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3566,7 +3572,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3580,7 +3586,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3594,7 +3600,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3608,7 +3614,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3622,7 +3628,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3636,7 +3642,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3650,7 +3656,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>374</v>
+        <v>352</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3664,7 +3670,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3678,7 +3684,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>377</v>
+        <v>320</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3692,7 +3698,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>378</v>
+        <v>318</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3703,10 +3709,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3720,7 +3726,7 @@
         <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3734,7 +3740,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3748,7 +3754,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3762,7 +3768,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3776,7 +3782,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3787,10 +3793,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D142" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3804,7 +3810,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3818,7 +3824,7 @@
         <v>259</v>
       </c>
       <c r="D144" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3832,7 +3838,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3846,7 +3852,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3860,7 +3866,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3874,7 +3880,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3888,7 +3894,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3902,7 +3908,7 @@
         <v>259</v>
       </c>
       <c r="D150" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3916,7 +3922,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3930,7 +3936,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3944,7 +3950,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>377</v>
+        <v>396</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3958,7 +3964,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -3972,7 +3978,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -3986,7 +3992,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4000,7 +4006,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4014,7 +4020,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4028,7 +4034,7 @@
         <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4042,7 +4048,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4056,7 +4062,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4070,7 +4076,7 @@
         <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4084,7 +4090,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4098,7 +4104,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4112,7 +4118,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>269</v>
+        <v>351</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4126,7 +4132,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>374</v>
+        <v>352</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4140,7 +4146,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>407</v>
+        <v>352</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4154,7 +4160,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4168,7 +4174,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>378</v>
+        <v>408</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4182,7 +4188,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>348</v>
+        <v>320</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4196,7 +4202,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>348</v>
+        <v>270</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4210,7 +4216,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>407</v>
+        <v>352</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4224,7 +4230,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4238,7 +4244,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4252,7 +4258,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4266,7 +4272,7 @@
         <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4280,7 +4286,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>318</v>
+        <v>413</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4294,7 +4300,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4308,7 +4314,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4322,7 +4328,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4336,7 +4342,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4350,7 +4356,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4364,7 +4370,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4378,7 +4384,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4392,7 +4398,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4406,7 +4412,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4420,7 +4426,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4434,7 +4440,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4448,7 +4454,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4459,10 +4465,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D190" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4476,7 +4482,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4487,10 +4493,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4504,7 +4510,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4518,7 +4524,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4529,10 +4535,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D195" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4543,10 +4549,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4557,10 +4563,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4574,7 +4580,7 @@
         <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4588,7 +4594,7 @@
         <v>259</v>
       </c>
       <c r="D199" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4602,7 +4608,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4616,7 +4622,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4630,7 +4636,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4644,7 +4650,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4658,7 +4664,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4672,7 +4678,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4683,10 +4689,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D206" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4700,7 +4706,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4714,7 +4720,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4728,7 +4734,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4742,7 +4748,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4756,7 +4762,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4770,7 +4776,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4784,7 +4790,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4798,7 +4804,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>447</v>
+        <v>408</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4812,7 +4818,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4826,7 +4832,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4840,7 +4846,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>348</v>
+        <v>449</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4854,7 +4860,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>318</v>
+        <v>450</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4868,7 +4874,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>348</v>
+        <v>270</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4882,7 +4888,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4896,7 +4902,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4907,10 +4913,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D222" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4924,7 +4930,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4938,7 +4944,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4952,7 +4958,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -4966,7 +4972,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -4980,7 +4986,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -4994,7 +5000,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5008,7 +5014,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5022,7 +5028,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5036,7 +5042,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5047,10 +5053,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D232" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5061,10 +5067,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D233" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5078,7 +5084,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5092,7 +5098,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5106,7 +5112,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5120,7 +5126,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>462</v>
+        <v>270</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5134,7 +5140,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5148,7 +5154,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5162,7 +5168,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>347</v>
+        <v>270</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5176,7 +5182,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>346</v>
+        <v>272</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5190,7 +5196,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5204,7 +5210,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5218,7 +5224,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5232,7 +5238,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5246,7 +5252,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5260,7 +5266,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5274,7 +5280,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5288,7 +5294,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5302,7 +5308,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5316,7 +5322,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5327,10 +5333,10 @@
         <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D252" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5344,7 +5350,7 @@
         <v>259</v>
       </c>
       <c r="D253" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5358,7 +5364,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5372,7 +5378,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5386,7 +5392,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
   </sheetData>
